--- a/data/trans_bre/P20B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Edad-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-61,98; 0,0</t>
+          <t>-62,69; -1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-48,49; 6,9</t>
+          <t>-49,56; 5,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-48,29; 7,16</t>
+          <t>-49,42; 4,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,49; 116,41</t>
+          <t>-91,77; 97,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,87; -0,66</t>
+          <t>-39,32; -1,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 0,51</t>
+          <t>-28,64; -0,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 7,76</t>
+          <t>-31,91; 8,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 2,5</t>
+          <t>-64,13; 4,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,59; 7,24</t>
+          <t>-90,72; 5,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,4; 47,77</t>
+          <t>-93,99; 7,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,13; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 5,33</t>
+          <t>-46,73; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 20,2</t>
+          <t>-24,64; 18,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-51,89; -5,32</t>
+          <t>-51,59; -3,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 19,86</t>
+          <t>-28,99; 20,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,25; 33,98</t>
+          <t>-82,69; 19,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,52; 105,18</t>
+          <t>-51,26; 91,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-87,74; -8,06</t>
+          <t>-85,71; -1,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 288,59</t>
+          <t>-65,17; 233,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 48,57</t>
+          <t>-6,56; 45,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 31,79</t>
+          <t>-16,1; 30,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 32,1</t>
+          <t>-26,59; 29,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 25,3</t>
+          <t>-16,49; 25,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 942,33</t>
+          <t>-33,24; 802,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 112,05</t>
+          <t>-28,25; 109,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,25; 143,55</t>
+          <t>-45,75; 112,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 97,23</t>
+          <t>-33,55; 104,47</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 31,37</t>
+          <t>-28,09; 31,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 29,65</t>
+          <t>-20,92; 29,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 27,01</t>
+          <t>-24,99; 28,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 11,44</t>
+          <t>-24,85; 11,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,13; 120,3</t>
+          <t>-47,1; 118,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 144,38</t>
+          <t>-45,02; 149,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 77,93</t>
+          <t>-43,87; 85,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,9; 43,94</t>
+          <t>-55,77; 47,44</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 33,04</t>
+          <t>-13,03; 32,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 22,18</t>
+          <t>-25,33; 23,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 43,18</t>
+          <t>-2,32; 44,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,97; -3,43</t>
+          <t>-37,75; -3,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,91; 351,02</t>
+          <t>-43,68; 279,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,48; 111,86</t>
+          <t>-53,88; 106,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 300,3</t>
+          <t>-15,21; 352,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-77,8; -8,72</t>
+          <t>-75,77; -7,39</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 21,76</t>
+          <t>-17,97; 21,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 14,2</t>
+          <t>-22,46; 13,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 25,57</t>
+          <t>-23,72; 24,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 18,32</t>
+          <t>-11,81; 18,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-77,95; 536,75</t>
+          <t>-78,96; 559,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-81,96; 205,1</t>
+          <t>-79,92; 199,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-58,24; 295,88</t>
+          <t>-65,74; 207,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 160,8</t>
+          <t>-38,24; 167,46</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 1,92</t>
+          <t>-14,9; 2,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 2,97</t>
+          <t>-13,11; 3,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 0,05</t>
+          <t>-18,99; 0,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -1,36</t>
+          <t>-18,38; -2,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 10,86</t>
+          <t>-47,18; 13,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 12,51</t>
+          <t>-37,91; 13,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 0,31</t>
+          <t>-48,1; 2,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,23; -4,93</t>
+          <t>-47,82; -6,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20B-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>13,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-62,69; -1,33</t>
+          <t>-58,55; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 5,78</t>
+          <t>-50,68; 5,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 4,31</t>
+          <t>-50,7; 3,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-91,77; 97,59</t>
+          <t>-93,66; 86,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-25,93</t>
+          <t>-22,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-78,23%</t>
+          <t>-77,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,32; -1,39</t>
+          <t>-39,22; -0,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,64; -0,81</t>
+          <t>-29,21; -0,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 8,06</t>
+          <t>-34,34; 8,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,13; 4,95</t>
+          <t>-56,65; 3,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-90,72; 5,26</t>
+          <t>-89,76; 11,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-93,99; 7,63</t>
+          <t>-91,82; 31,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-93,13; —</t>
+          <t>-93,36; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-3,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,66%</t>
+          <t>-13,51%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 2,7</t>
+          <t>-46,63; 4,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 18,81</t>
+          <t>-23,17; 18,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-51,59; -3,11</t>
+          <t>-53,22; -4,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 20,41</t>
+          <t>-29,16; 15,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,69; 19,15</t>
+          <t>-83,0; 36,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,26; 91,13</t>
+          <t>-49,18; 100,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,71; -1,41</t>
+          <t>-86,51; -2,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,17; 233,05</t>
+          <t>-68,44; 151,21</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 45,22</t>
+          <t>-4,78; 44,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 30,29</t>
+          <t>-14,2; 31,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 29,97</t>
+          <t>-23,97; 31,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 25,31</t>
+          <t>-18,32; 23,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,24; 802,02</t>
+          <t>-24,97; 776,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 109,57</t>
+          <t>-26,7; 112,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 112,31</t>
+          <t>-43,34; 131,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 104,47</t>
+          <t>-34,3; 84,49</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,91</t>
+          <t>-3,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-21,36%</t>
+          <t>-8,95%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 31,57</t>
+          <t>-28,04; 33,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 29,44</t>
+          <t>-18,82; 32,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 28,02</t>
+          <t>-25,15; 27,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 11,66</t>
+          <t>-20,95; 14,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 118,12</t>
+          <t>-45,02; 131,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,02; 149,49</t>
+          <t>-41,42; 176,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 85,21</t>
+          <t>-43,25; 85,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-55,77; 47,44</t>
+          <t>-50,6; 56,91</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-20,28</t>
+          <t>-18,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-48,86%</t>
+          <t>-46,68%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 32,14</t>
+          <t>-11,68; 34,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 23,14</t>
+          <t>-27,01; 22,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 44,94</t>
+          <t>-3,21; 44,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,75; -3,26</t>
+          <t>-36,57; 0,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 279,96</t>
+          <t>-39,38; 414,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,88; 106,79</t>
+          <t>-56,45; 125,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 352,43</t>
+          <t>-14,67; 310,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,77; -7,39</t>
+          <t>-75,76; 2,93</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,34</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 21,09</t>
+          <t>-17,79; 24,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 13,8</t>
+          <t>-23,26; 14,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 24,24</t>
+          <t>-22,49; 26,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 18,3</t>
+          <t>-9,18; 20,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-78,96; 559,84</t>
+          <t>-75,24; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-79,92; 199,13</t>
+          <t>-79,43; 323,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-65,74; 207,92</t>
+          <t>-64,11; 234,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 167,46</t>
+          <t>-34,4; 201,44</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-10,13</t>
+          <t>-9,9</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-30,59%</t>
+          <t>-29,79%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 2,69</t>
+          <t>-14,99; 2,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 3,2</t>
+          <t>-13,55; 3,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 0,61</t>
+          <t>-18,67; -0,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -2,41</t>
+          <t>-18,05; -1,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 13,67</t>
+          <t>-47,19; 14,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,91; 13,89</t>
+          <t>-39,16; 15,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 2,99</t>
+          <t>-46,47; -0,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -6,54</t>
+          <t>-47,21; -3,06</t>
         </is>
       </c>
     </row>
